--- a/data-raw/data.xlsx
+++ b/data-raw/data.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE665DCD-B930-49F6-B5C8-B54E4E7EA6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="4380" yWindow="2430" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Φύλλο1" sheetId="1" r:id="rId1"/>
@@ -174,7 +175,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -225,7 +226,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -502,19 +503,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -534,7 +535,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="196.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="196.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -545,7 +546,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>33</v>
@@ -554,7 +555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -574,7 +575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -594,7 +595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -614,7 +615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -634,7 +635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -654,7 +655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
@@ -674,7 +675,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
@@ -694,7 +695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
@@ -714,7 +715,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>39</v>
       </c>
@@ -734,7 +735,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -754,7 +755,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>30</v>
       </c>
@@ -774,7 +775,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
